--- a/basedatos_partidas/salida/descompuestos/05.04.01.130.xlsx
+++ b/basedatos_partidas/salida/descompuestos/05.04.01.130.xlsx
@@ -584,10 +584,10 @@
         <v>0.2</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>30.21</v>
+        <v>30.25</v>
       </c>
     </row>
     <row r="13">
@@ -769,7 +769,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>42.38</v>
+        <v>42.42</v>
       </c>
       <c r="H22" t="n">
         <v>0.42</v>
@@ -788,7 +788,7 @@
       </c>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="5" t="n">
-        <v>42.8</v>
+        <v>42.84</v>
       </c>
     </row>
   </sheetData>
